--- a/feedback_forms/016_flight_punctuality_and_delay_report_form--feedback_forms.xlsx
+++ b/feedback_forms/016_flight_punctuality_and_delay_report_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'flight_report',_'name':_'flight_report'}</t>
+          <t>flight_report</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'flight_report', 'name': 'Flight Report'}</t>
+          <t>Flight Report</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'delay_report',_'name':_'delay_report'}</t>
+          <t>delay_report</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'delay_report', 'name': 'Delay Report'}</t>
+          <t>Delay Report</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'flight_number',_'name':_'flight_number'}</t>
+          <t>flight_number</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'flight_number', 'name': 'Flight Number'}</t>
+          <t>Flight Number</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'flight_date',_'name':_'flight_date'}</t>
+          <t>flight_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'flight_date', 'name': 'Flight Date'}</t>
+          <t>Flight Date</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'flight_status',_'name':_'flight_status'}</t>
+          <t>flight_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'flight_status', 'name': 'Flight Status'}</t>
+          <t>Flight Status</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'flight_cancellation_reason',_'name':_'flight_cancellation_reason'}</t>
+          <t>flight_cancellation_reason</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'flight_cancellation_reason', 'name': 'Flight Cancellation Reason'}</t>
+          <t>Flight Cancellation Reason</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'on_time',_'name':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'on_time', 'name': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'delayed',_'name':_'delayed'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'delayed', 'name': 'Delayed'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'cancelled',_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'cancelled', 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'diverted',_'name':_'diverted'}</t>
+          <t>diverted</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'diverted', 'name': 'Diverted'}</t>
+          <t>Diverted</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'weather',_'name':_'weather'}</t>
+          <t>weather</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'weather', 'name': 'Weather'}</t>
+          <t>Weather</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'mechanical',_'name':_'mechanical'}</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'mechanical', 'name': 'Mechanical'}</t>
+          <t>Mechanical</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'air_traffic',_'name':_'air_traffic'}</t>
+          <t>air_traffic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 'air_traffic', 'name': 'Air Traffic'}</t>
+          <t>Air Traffic</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'ground_traffic',_'name':_'ground_traffic'}</t>
+          <t>ground_traffic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'ground_traffic', 'name': 'Ground Traffic'}</t>
+          <t>Ground Traffic</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'other',_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 'other', 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'primary_contact',_'name':_'primary_contact'}</t>
+          <t>primary_contact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 'primary_contact', 'name': 'Primary Contact'}</t>
+          <t>Primary Contact</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'secondary_contact',_'name':_'secondary_contact'}</t>
+          <t>secondary_contact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 'secondary_contact', 'name': 'Secondary Contact'}</t>
+          <t>Secondary Contact</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'support_team',_'name':_'support_team'}</t>
+          <t>support_team</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 'support_team', 'name': 'Support Team'}</t>
+          <t>Support Team</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'submit_now',_'name':_'submit_now'}</t>
+          <t>submit_now</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 'submit_now', 'name': 'Submit Now'}</t>
+          <t>Submit Now</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'submit_later',_'name':_'submit_later'}</t>
+          <t>submit_later</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 'submit_later', 'name': 'Submit Later'}</t>
+          <t>Submit Later</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'submit_now',_'name':_'submit_now'}</t>
+          <t>submit_now</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 'submit_now', 'name': 'Submit Now'}</t>
+          <t>Submit Now</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'submit_later',_'name':_'submit_later'}</t>
+          <t>submit_later</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 'submit_later', 'name': 'Submit Later'}</t>
+          <t>Submit Later</t>
         </is>
       </c>
     </row>
